--- a/data/trans_orig/P27_1-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P27_1-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo que pasa en ambientes cargados de humo de tabaco durante los días de diario en 2007</t>
+          <t>Población según el tiempo que pasa en ambientes cargados de humo de tabaco durante los días de diario en 2007 (tasa de respuesta: 94,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>50959</t>
+          <t>50419</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>82373</t>
+          <t>82394</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17884</t>
+          <t>17372</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37591</t>
+          <t>37098</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>74762</t>
+          <t>73753</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>111927</t>
+          <t>111324</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>113215</t>
+          <t>111461</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>152302</t>
+          <t>151243</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>80829</t>
+          <t>80171</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>116289</t>
+          <t>117771</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>201855</t>
+          <t>202546</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>254972</t>
+          <t>256089</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,79%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>237719</t>
+          <t>236065</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>289230</t>
+          <t>285928</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>267840</t>
+          <t>266907</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>319189</t>
+          <t>318535</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>520463</t>
+          <t>526640</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>588604</t>
+          <t>593005</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,84%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>172716</t>
+          <t>174268</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>219265</t>
+          <t>221667</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>198304</t>
+          <t>196664</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>244208</t>
+          <t>244156</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>386893</t>
+          <t>381565</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>451548</t>
+          <t>449331</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,73%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>61758</t>
+          <t>60413</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>97485</t>
+          <t>95585</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>37489</t>
+          <t>38442</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>66256</t>
+          <t>66752</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>107681</t>
+          <t>109742</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>150136</t>
+          <t>152469</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>176597</t>
+          <t>179311</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>229678</t>
+          <t>229541</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>112730</t>
+          <t>113748</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>157578</t>
+          <t>157648</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>301830</t>
+          <t>301471</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>374683</t>
+          <t>373841</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,07%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>312147</t>
+          <t>310283</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>370739</t>
+          <t>372174</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>349093</t>
+          <t>350640</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>410851</t>
+          <t>409105</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>678355</t>
+          <t>678532</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>763131</t>
+          <t>760274</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>40,82%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>273034</t>
+          <t>273317</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>331469</t>
+          <t>331001</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>344856</t>
+          <t>344331</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>405233</t>
+          <t>406636</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>634940</t>
+          <t>633262</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>723240</t>
+          <t>718806</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,59%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33296</t>
+          <t>34089</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>61553</t>
+          <t>61280</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15928</t>
+          <t>15433</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>34719</t>
+          <t>32940</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>53390</t>
+          <t>55653</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>86627</t>
+          <t>88893</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>112646</t>
+          <t>112216</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>155783</t>
+          <t>155369</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>62315</t>
+          <t>62405</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>94289</t>
+          <t>94423</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>183779</t>
+          <t>185263</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>240420</t>
+          <t>238290</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,15%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>228443</t>
+          <t>231283</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>279762</t>
+          <t>283688</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>234883</t>
+          <t>234659</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>284186</t>
+          <t>283392</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>478486</t>
+          <t>477392</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>551372</t>
+          <t>548978</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>41,83%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>193175</t>
+          <t>192863</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>243330</t>
+          <t>239652</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>278840</t>
+          <t>275360</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>327358</t>
+          <t>326545</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>481828</t>
+          <t>480327</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>553608</t>
+          <t>549357</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>41,85%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>56312</t>
+          <t>56982</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>88251</t>
+          <t>87063</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>40495</t>
+          <t>42064</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>69787</t>
+          <t>70410</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>106209</t>
+          <t>106264</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>148275</t>
+          <t>149400</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>163722</t>
+          <t>163601</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>210555</t>
+          <t>208816</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>134588</t>
+          <t>136468</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>180635</t>
+          <t>182764</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>312365</t>
+          <t>310192</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>377173</t>
+          <t>377165</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>326132</t>
+          <t>325115</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>380939</t>
+          <t>381596</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>356404</t>
+          <t>352594</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>419750</t>
+          <t>417924</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>700374</t>
+          <t>695956</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>778619</t>
+          <t>777286</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>41,9%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>246779</t>
+          <t>245927</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>299788</t>
+          <t>296413</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>347992</t>
+          <t>346426</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>408487</t>
+          <t>408587</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>608329</t>
+          <t>609881</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>690266</t>
+          <t>691938</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,3%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>230451</t>
+          <t>231422</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>293470</t>
+          <t>296676</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>131153</t>
+          <t>131336</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>182464</t>
+          <t>180018</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>375689</t>
+          <t>377526</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>456635</t>
+          <t>455145</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>603150</t>
+          <t>611422</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>701917</t>
+          <t>700905</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>430971</t>
+          <t>426246</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>508770</t>
+          <t>506480</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1063415</t>
+          <t>1067679</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1185269</t>
+          <t>1183049</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,71%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1156062</t>
+          <t>1156166</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1263928</t>
+          <t>1261130</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1263771</t>
+          <t>1259286</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1374037</t>
+          <t>1369316</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2449376</t>
+          <t>2455889</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2609189</t>
+          <t>2611657</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,3%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>938260</t>
+          <t>935564</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1043768</t>
+          <t>1040713</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1215043</t>
+          <t>1222396</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1328197</t>
+          <t>1334990</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2178979</t>
+          <t>2188542</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2336426</t>
+          <t>2337659</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,96%</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo que pasa en ambientes cargados de humo de tabaco durante los días de diario en 2012</t>
+          <t>Población según el tiempo que pasa en ambientes cargados de humo de tabaco durante los días de diario en 2012 (tasa de respuesta: 96,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>6419</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21725</t>
+          <t>20769</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4027</t>
+          <t>4093</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16499</t>
+          <t>16121</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12992</t>
+          <t>13258</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31441</t>
+          <t>29816</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26586</t>
+          <t>25856</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50724</t>
+          <t>50596</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18143</t>
+          <t>18328</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39522</t>
+          <t>40222</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>48858</t>
+          <t>49641</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>82205</t>
+          <t>81748</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>68196</t>
+          <t>66632</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>102614</t>
+          <t>100633</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>52701</t>
+          <t>53389</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>86806</t>
+          <t>84700</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>130014</t>
+          <t>129138</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>176078</t>
+          <t>176100</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>543869</t>
+          <t>545601</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>586001</t>
+          <t>587297</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>562188</t>
+          <t>561720</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>602140</t>
+          <t>600859</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1119434</t>
+          <t>1118235</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1176933</t>
+          <t>1177637</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,96%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15410</t>
+          <t>15051</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>36122</t>
+          <t>35384</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10462</t>
+          <t>10771</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27174</t>
+          <t>29191</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>29544</t>
+          <t>30477</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>56139</t>
+          <t>56261</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36275</t>
+          <t>35765</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64339</t>
+          <t>64743</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30618</t>
+          <t>29339</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55928</t>
+          <t>55563</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>71279</t>
+          <t>70237</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>110040</t>
+          <t>109792</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>109349</t>
+          <t>111315</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>154506</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>79038</t>
+          <t>80332</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>118744</t>
+          <t>116113</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>202337</t>
+          <t>199092</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>260704</t>
+          <t>258278</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,73%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>780638</t>
+          <t>777111</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>833872</t>
+          <t>828225</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>77,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>840244</t>
+          <t>839874</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>888254</t>
+          <t>886444</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1632523</t>
+          <t>1631470</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1701674</t>
+          <t>1703329</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,97%</t>
         </is>
       </c>
     </row>
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5716</t>
+          <t>5695</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19276</t>
+          <t>19329</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3513</t>
+          <t>3480</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15091</t>
+          <t>16316</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11311</t>
+          <t>11008</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>28767</t>
+          <t>28475</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12915</t>
+          <t>13927</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>33000</t>
+          <t>33372</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12842</t>
+          <t>12541</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>31774</t>
+          <t>32687</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>30172</t>
+          <t>29185</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>57952</t>
+          <t>57031</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>62385</t>
+          <t>64193</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>97007</t>
+          <t>100535</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>70376</t>
+          <t>70939</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>107656</t>
+          <t>108147</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>142947</t>
+          <t>140168</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>193540</t>
+          <t>190624</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,62%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>611311</t>
+          <t>610610</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>651773</t>
+          <t>650745</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>628041</t>
+          <t>628152</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>671087</t>
+          <t>670464</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1251415</t>
+          <t>1253356</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1309582</t>
+          <t>1311282</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,84%</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13408</t>
+          <t>12974</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30358</t>
+          <t>30635</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13291</t>
+          <t>13106</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31496</t>
+          <t>32276</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>30469</t>
+          <t>32250</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>55309</t>
+          <t>57622</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>31335</t>
+          <t>30016</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>56446</t>
+          <t>57002</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34771</t>
+          <t>35690</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>62736</t>
+          <t>60969</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>72769</t>
+          <t>70715</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>108531</t>
+          <t>107556</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>125489</t>
+          <t>124314</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>172497</t>
+          <t>169936</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>93407</t>
+          <t>96512</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>135874</t>
+          <t>139414</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>231756</t>
+          <t>229912</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>296179</t>
+          <t>293413</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>15,99%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>645596</t>
+          <t>646560</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>696256</t>
+          <t>699031</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>747411</t>
+          <t>743034</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>797721</t>
+          <t>793736</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1402052</t>
+          <t>1405043</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1477394</t>
+          <t>1478579</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>76,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,56%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>52462</t>
+          <t>53218</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>83517</t>
+          <t>84891</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>40986</t>
+          <t>42059</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>71280</t>
+          <t>71573</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>102997</t>
+          <t>101897</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>146866</t>
+          <t>147136</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>126216</t>
+          <t>126328</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>175436</t>
+          <t>176381</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>113241</t>
+          <t>114838</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>157386</t>
+          <t>163163</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>251845</t>
+          <t>255200</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>318310</t>
+          <t>320951</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>396358</t>
+          <t>398574</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>479302</t>
+          <t>479198</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,7 +6327,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>333036</t>
+          <t>331061</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>404547</t>
+          <t>406838</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>753759</t>
+          <t>752929</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>863059</t>
+          <t>861708</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,75%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2627151</t>
+          <t>2629858</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2723208</t>
+          <t>2721983</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2822899</t>
+          <t>2825308</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2914351</t>
+          <t>2918566</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>5479522</t>
+          <t>5480360</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>5610442</t>
+          <t>5602343</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>82,88%</t>
         </is>
       </c>
     </row>
@@ -6692,7 +6692,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo que pasa en ambientes cargados de humo de tabaco durante los días de diario en 2016</t>
+          <t>Población según el tiempo que pasa en ambientes cargados de humo de tabaco durante los días de diario en 2016 (tasa de respuesta: 97,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7152</t>
+          <t>7148</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23723</t>
+          <t>24100</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3670</t>
+          <t>3759</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15648</t>
+          <t>17526</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13550</t>
+          <t>12988</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33975</t>
+          <t>32393</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28854</t>
+          <t>29422</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52214</t>
+          <t>53494</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12040</t>
+          <t>12193</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30729</t>
+          <t>30597</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45110</t>
+          <t>44330</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>76538</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>96356</t>
+          <t>99184</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>137151</t>
+          <t>137074</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>69286</t>
+          <t>70390</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>103762</t>
+          <t>104765</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>178824</t>
+          <t>177334</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>234138</t>
+          <t>233886</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,91%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>459813</t>
+          <t>456803</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>504702</t>
+          <t>500844</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>76,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>519420</t>
+          <t>519885</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>560004</t>
+          <t>557911</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>989281</t>
+          <t>988521</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1050056</t>
+          <t>1048644</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,29%</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7456,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10446</t>
+          <t>10380</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>28947</t>
+          <t>27689</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14020</t>
+          <t>12820</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31984</t>
+          <t>31231</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>26846</t>
+          <t>27261</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>52469</t>
+          <t>53875</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40721</t>
+          <t>39819</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>72303</t>
+          <t>70408</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30313</t>
+          <t>30766</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>56843</t>
+          <t>56144</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>79372</t>
+          <t>77045</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>116440</t>
+          <t>116732</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>155788</t>
+          <t>154650</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>205425</t>
+          <t>205195</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>138291</t>
+          <t>137118</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>187815</t>
+          <t>184664</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>307083</t>
+          <t>303790</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>377186</t>
+          <t>375093</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,43%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>732103</t>
+          <t>731285</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>788619</t>
+          <t>788082</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>770059</t>
+          <t>771212</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>826423</t>
+          <t>827675</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1520436</t>
+          <t>1520080</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1598514</t>
+          <t>1600935</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,66%</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>29118</t>
+          <t>29742</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>55043</t>
+          <t>56672</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22801</t>
+          <t>23328</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>46557</t>
+          <t>46218</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>58821</t>
+          <t>58393</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>94184</t>
+          <t>94372</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>75741</t>
+          <t>74866</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>114328</t>
+          <t>113442</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>81392</t>
+          <t>82978</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>120068</t>
+          <t>121168</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>168772</t>
+          <t>165923</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>219589</t>
+          <t>218531</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,47%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>148712</t>
+          <t>148152</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>196707</t>
+          <t>192876</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>141511</t>
+          <t>139332</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>184198</t>
+          <t>186187</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>302114</t>
+          <t>304202</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>367543</t>
+          <t>370619</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,54%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>409938</t>
+          <t>416715</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>468182</t>
+          <t>471337</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>55,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>439169</t>
+          <t>437434</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>492765</t>
+          <t>492739</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>868070</t>
+          <t>868867</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>944629</t>
+          <t>949106</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>62,84%</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6109</t>
+          <t>6330</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20829</t>
+          <t>21172</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13153</t>
+          <t>13344</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31889</t>
+          <t>31472</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22851</t>
+          <t>23817</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>45428</t>
+          <t>46421</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>26817</t>
+          <t>26645</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>50531</t>
+          <t>49619</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>28587</t>
+          <t>29546</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>54019</t>
+          <t>56164</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>62166</t>
+          <t>62119</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>96845</t>
+          <t>98625</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>114363</t>
+          <t>114939</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>158287</t>
+          <t>158521</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>108379</t>
+          <t>107822</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>151955</t>
+          <t>150974</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>237822</t>
+          <t>233196</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>297871</t>
+          <t>300177</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>703272</t>
+          <t>698884</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>752137</t>
+          <t>747710</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>794196</t>
+          <t>792227</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>844849</t>
+          <t>844308</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1508118</t>
+          <t>1508615</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1576835</t>
+          <t>1580388</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>82,28%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>66539</t>
+          <t>66590</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>103876</t>
+          <t>106513</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>66485</t>
+          <t>66442</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>103589</t>
+          <t>103984</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>143899</t>
+          <t>144016</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>196297</t>
+          <t>196546</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,7 +9248,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>193822</t>
+          <t>198356</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>254674</t>
+          <t>253029</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>176981</t>
+          <t>177889</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>233260</t>
+          <t>234205</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>385575</t>
+          <t>385127</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>467839</t>
+          <t>471062</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>565380</t>
+          <t>563243</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>654903</t>
+          <t>653347</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>498387</t>
+          <t>497471</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>582074</t>
+          <t>583278</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1084708</t>
+          <t>1081251</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1212690</t>
+          <t>1211490</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,89%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2358449</t>
+          <t>2360253</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2463320</t>
+          <t>2463879</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2573849</t>
+          <t>2570296</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2674006</t>
+          <t>2671740</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>4950913</t>
+          <t>4951247</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>5095819</t>
+          <t>5106262</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9592,7 +9592,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,4%</t>
         </is>
       </c>
     </row>
@@ -9769,7 +9769,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo que pasa en ambientes cargados de humo de tabaco durante los días de diario en 2023</t>
+          <t>Población según el tiempo que pasa en ambientes cargados de humo de tabaco durante los días de diario en 2023 (tasa de respuesta: 99,59%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9964,12 +9964,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1604</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8610</t>
+          <t>8319</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9979,12 +9979,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>824</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10019,7 +10019,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1594</t>
+          <t>1586</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8593</t>
+          <t>8611</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21633</t>
+          <t>22142</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43932</t>
+          <t>44224</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10092,12 +10092,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14077</t>
+          <t>13321</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29586</t>
+          <t>29738</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39830</t>
+          <t>39420</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>67255</t>
+          <t>67967</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -10190,12 +10190,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>47415</t>
+          <t>48100</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>86396</t>
+          <t>87775</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10205,12 +10205,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>38839</t>
+          <t>39293</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>60369</t>
+          <t>59881</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10240,12 +10240,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>93457</t>
+          <t>94654</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>136980</t>
+          <t>140641</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10275,12 +10275,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,78%</t>
         </is>
       </c>
     </row>
@@ -10303,12 +10303,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>508942</t>
+          <t>508907</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>552897</t>
+          <t>551607</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>588531</t>
+          <t>587863</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>614014</t>
+          <t>613063</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10353,12 +10353,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1108809</t>
+          <t>1106049</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1161410</t>
+          <t>1159500</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>88,89%</t>
         </is>
       </c>
     </row>
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>513</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7314</t>
+          <t>7166</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5574</t>
+          <t>5748</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17446</t>
+          <t>18030</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10583,47 +10583,47 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>12475</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>6576</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>20454</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
           <t>0,59%</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>12475</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>7000</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>20607</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -10646,12 +10646,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19287</t>
+          <t>17441</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59182</t>
+          <t>58109</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10661,12 +10661,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25324</t>
+          <t>24676</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46727</t>
+          <t>46958</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>49295</t>
+          <t>50733</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>96619</t>
+          <t>97828</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -10759,12 +10759,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53317</t>
+          <t>49424</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>141228</t>
+          <t>141893</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10774,12 +10774,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>77998</t>
+          <t>77206</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>110362</t>
+          <t>111951</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>125975</t>
+          <t>130452</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>232442</t>
+          <t>235226</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,04%</t>
         </is>
       </c>
     </row>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>985363</t>
+          <t>986989</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1103786</t>
+          <t>1114040</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10887,12 +10887,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>793090</t>
+          <t>791532</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>831387</t>
+          <t>831961</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10922,12 +10922,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1797957</t>
+          <t>1798709</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1942914</t>
+          <t>1940738</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10957,12 +10957,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,1%</t>
         </is>
       </c>
     </row>
@@ -11102,12 +11102,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1846</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11887</t>
+          <t>11699</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11117,12 +11117,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3192</t>
+          <t>3104</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19741</t>
+          <t>17482</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11152,12 +11152,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>6915</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24235</t>
+          <t>24518</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -11215,12 +11215,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29682</t>
+          <t>29239</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>59853</t>
+          <t>60063</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11230,12 +11230,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13541</t>
+          <t>16235</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>49253</t>
+          <t>48398</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11265,12 +11265,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>46595</t>
+          <t>46490</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>96868</t>
+          <t>97061</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11300,12 +11300,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -11328,12 +11328,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>102160</t>
+          <t>98950</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>151668</t>
+          <t>152439</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>45679</t>
+          <t>48364</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>131917</t>
+          <t>132542</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11378,12 +11378,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>139142</t>
+          <t>145391</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>268738</t>
+          <t>268597</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11413,12 +11413,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -11441,12 +11441,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>502856</t>
+          <t>500568</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>558269</t>
+          <t>559251</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11456,12 +11456,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>743131</t>
+          <t>746354</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>864795</t>
+          <t>866535</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11491,12 +11491,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1264355</t>
+          <t>1267787</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1438498</t>
+          <t>1444096</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11526,12 +11526,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>88,31%</t>
         </is>
       </c>
     </row>
@@ -11671,12 +11671,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11046</t>
+          <t>11008</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27688</t>
+          <t>25848</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11691,7 +11691,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6372</t>
+          <t>6813</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22268</t>
+          <t>22787</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11721,47 +11721,47 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>29529</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>20675</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>41226</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
           <t>2,04%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>29529</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>20188</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>42880</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -11784,12 +11784,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>45898</t>
+          <t>46577</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>84803</t>
+          <t>83871</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34891</t>
+          <t>35362</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>60783</t>
+          <t>60471</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11834,12 +11834,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>88544</t>
+          <t>87643</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>135595</t>
+          <t>134581</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11869,12 +11869,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -11897,12 +11897,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>81486</t>
+          <t>82482</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>126710</t>
+          <t>130280</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11912,12 +11912,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>74544</t>
+          <t>74436</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>114132</t>
+          <t>113784</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11947,12 +11947,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>167217</t>
+          <t>169394</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>226672</t>
+          <t>230296</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,41%</t>
         </is>
       </c>
     </row>
@@ -12010,12 +12010,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>715148</t>
+          <t>714389</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>773800</t>
+          <t>770859</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12025,12 +12025,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>912511</t>
+          <t>913970</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>969161</t>
+          <t>967367</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12060,12 +12060,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1644156</t>
+          <t>1642346</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1725839</t>
+          <t>1723496</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12095,12 +12095,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,41%</t>
         </is>
       </c>
     </row>
@@ -12240,12 +12240,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>19218</t>
+          <t>19269</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>39935</t>
+          <t>40439</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12260,7 +12260,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>21213</t>
+          <t>21520</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>44356</t>
+          <t>45686</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12290,12 +12290,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>45346</t>
+          <t>45043</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>76111</t>
+          <t>78476</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12330,7 +12330,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -12353,12 +12353,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>134693</t>
+          <t>136284</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>210784</t>
+          <t>211155</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12368,12 +12368,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>107336</t>
+          <t>108165</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>159480</t>
+          <t>160076</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12403,12 +12403,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>258849</t>
+          <t>262268</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>356641</t>
+          <t>353856</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12438,12 +12438,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -12466,12 +12466,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>307638</t>
+          <t>298510</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>449843</t>
+          <t>446509</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12481,12 +12481,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>271994</t>
+          <t>269730</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>374458</t>
+          <t>374290</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12516,7 +12516,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>620064</t>
+          <t>629137</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>800664</t>
+          <t>805738</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12551,12 +12551,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -12579,12 +12579,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2780032</t>
+          <t>2779826</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2995686</t>
+          <t>2985654</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12599,7 +12599,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3095374</t>
+          <t>3092690</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3242677</t>
+          <t>3237998</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>5894850</t>
+          <t>5893546</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6144802</t>
+          <t>6131086</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,5%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P27_1-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P27_1-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>50419</t>
+          <t>51068</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>82394</t>
+          <t>82156</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17372</t>
+          <t>17232</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37098</t>
+          <t>36957</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>73753</t>
+          <t>72793</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>111324</t>
+          <t>109888</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>111461</t>
+          <t>110887</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>151243</t>
+          <t>151683</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>80171</t>
+          <t>78993</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>117771</t>
+          <t>117696</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>202546</t>
+          <t>205753</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>256089</t>
+          <t>261275</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,2%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>236065</t>
+          <t>237629</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>285928</t>
+          <t>287625</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>266907</t>
+          <t>268789</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>318535</t>
+          <t>320650</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>526640</t>
+          <t>519997</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>593005</t>
+          <t>596262</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>46,09%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>174268</t>
+          <t>172268</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>221667</t>
+          <t>222473</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>196664</t>
+          <t>196885</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>244156</t>
+          <t>243960</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>381565</t>
+          <t>380392</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>449331</t>
+          <t>451218</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,88%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>60413</t>
+          <t>62399</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>95585</t>
+          <t>99064</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38442</t>
+          <t>37213</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>66752</t>
+          <t>65458</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>109742</t>
+          <t>108266</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>152469</t>
+          <t>152561</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>179311</t>
+          <t>175704</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>229541</t>
+          <t>225691</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>113748</t>
+          <t>112869</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>157648</t>
+          <t>158279</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>301471</t>
+          <t>305126</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>373841</t>
+          <t>371131</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,92%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>310283</t>
+          <t>313880</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>372174</t>
+          <t>375134</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>350640</t>
+          <t>349926</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>409105</t>
+          <t>411170</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>678532</t>
+          <t>674005</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>760274</t>
+          <t>764406</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>41,04%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>273317</t>
+          <t>274328</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>331001</t>
+          <t>332780</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>344331</t>
+          <t>342978</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>406636</t>
+          <t>402813</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>633262</t>
+          <t>632626</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>718806</t>
+          <t>719015</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>38,6%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34089</t>
+          <t>34088</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>61280</t>
+          <t>61979</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15433</t>
+          <t>15447</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>32940</t>
+          <t>33189</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>55653</t>
+          <t>54223</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>88893</t>
+          <t>86619</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>112216</t>
+          <t>114483</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>155369</t>
+          <t>155733</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>62405</t>
+          <t>61692</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>94423</t>
+          <t>95126</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>185263</t>
+          <t>185364</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>238290</t>
+          <t>238317</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,16%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>231283</t>
+          <t>229648</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>283688</t>
+          <t>281245</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>234659</t>
+          <t>231932</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>283392</t>
+          <t>279983</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>477392</t>
+          <t>480311</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>548978</t>
+          <t>553666</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>42,18%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>192863</t>
+          <t>193879</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>239652</t>
+          <t>241082</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>275360</t>
+          <t>277648</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>326545</t>
+          <t>328617</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>480327</t>
+          <t>484653</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>549357</t>
+          <t>557752</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>42,49%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>56982</t>
+          <t>55560</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>87063</t>
+          <t>89046</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>42064</t>
+          <t>40547</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>70410</t>
+          <t>69014</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>106264</t>
+          <t>102524</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>149400</t>
+          <t>146364</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>163601</t>
+          <t>160058</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>208816</t>
+          <t>206325</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>136468</t>
+          <t>135435</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>182764</t>
+          <t>183696</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>310192</t>
+          <t>312925</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>377165</t>
+          <t>376542</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,3%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>325115</t>
+          <t>325251</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>381596</t>
+          <t>380074</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>352594</t>
+          <t>354071</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>417924</t>
+          <t>415626</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>695956</t>
+          <t>696908</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>777286</t>
+          <t>780767</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>42,08%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>245927</t>
+          <t>245794</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>296413</t>
+          <t>298436</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>346426</t>
+          <t>345045</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>408587</t>
+          <t>406753</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>609881</t>
+          <t>609321</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>691938</t>
+          <t>686918</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,02%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>231422</t>
+          <t>230739</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>296676</t>
+          <t>293929</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>131336</t>
+          <t>130682</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>180018</t>
+          <t>179420</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>377526</t>
+          <t>377960</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>455145</t>
+          <t>457396</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>611422</t>
+          <t>607745</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>700905</t>
+          <t>696179</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>426246</t>
+          <t>429423</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>506480</t>
+          <t>507219</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1067679</t>
+          <t>1056532</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1183049</t>
+          <t>1180308</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,66%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1156166</t>
+          <t>1160390</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1261130</t>
+          <t>1266234</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1259286</t>
+          <t>1261735</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1369316</t>
+          <t>1367614</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2455889</t>
+          <t>2449392</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2611657</t>
+          <t>2600228</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,11%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>935564</t>
+          <t>935538</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1040713</t>
+          <t>1037481</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1222396</t>
+          <t>1216869</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1334990</t>
+          <t>1328671</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2188542</t>
+          <t>2190908</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2337659</t>
+          <t>2335832</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>36,93%</t>
         </is>
       </c>
     </row>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6419</t>
+          <t>7095</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20769</t>
+          <t>20978</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4093</t>
+          <t>3889</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16121</t>
+          <t>15419</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13258</t>
+          <t>13253</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29816</t>
+          <t>30984</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25856</t>
+          <t>25959</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50596</t>
+          <t>52511</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18328</t>
+          <t>18420</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40222</t>
+          <t>37648</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>49641</t>
+          <t>49369</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>81748</t>
+          <t>82658</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>66632</t>
+          <t>67817</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>100633</t>
+          <t>103558</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>53389</t>
+          <t>52833</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>84700</t>
+          <t>86519</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>129138</t>
+          <t>128256</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>176100</t>
+          <t>177231</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,79%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>545601</t>
+          <t>545827</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>587297</t>
+          <t>586866</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>561720</t>
+          <t>561402</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>600859</t>
+          <t>601637</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1118235</t>
+          <t>1122111</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1177637</t>
+          <t>1178896</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>85,05%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15051</t>
+          <t>13615</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35384</t>
+          <t>33605</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10771</t>
+          <t>10589</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29191</t>
+          <t>27924</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,47 +4429,47 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>41370</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>30532</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>58113</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
           <t>2,86%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>41370</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>30477</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>56261</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35765</t>
+          <t>34993</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64743</t>
+          <t>61968</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29339</t>
+          <t>29174</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55563</t>
+          <t>55204</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>70237</t>
+          <t>72317</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>109792</t>
+          <t>111911</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>111315</t>
+          <t>113167</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>154506</t>
+          <t>159985</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>80332</t>
+          <t>79296</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>116113</t>
+          <t>117136</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>199092</t>
+          <t>198623</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>258278</t>
+          <t>259004</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,77%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>777111</t>
+          <t>773242</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>828225</t>
+          <t>828473</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>839874</t>
+          <t>840796</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>886444</t>
+          <t>886944</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1631470</t>
+          <t>1630163</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1703329</t>
+          <t>1704785</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>84,05%</t>
         </is>
       </c>
     </row>
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5695</t>
+          <t>5766</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19329</t>
+          <t>18988</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3480</t>
+          <t>3162</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16316</t>
+          <t>15230</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11008</t>
+          <t>11344</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>28475</t>
+          <t>28911</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13927</t>
+          <t>13240</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>33372</t>
+          <t>33424</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12541</t>
+          <t>12659</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32687</t>
+          <t>33531</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>29185</t>
+          <t>29199</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>57031</t>
+          <t>57407</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>64193</t>
+          <t>62817</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>100535</t>
+          <t>95145</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>70939</t>
+          <t>71532</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>108147</t>
+          <t>107939</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>140168</t>
+          <t>143556</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>190624</t>
+          <t>193442</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,81%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>610610</t>
+          <t>612350</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>650745</t>
+          <t>650886</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>628152</t>
+          <t>630624</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>670464</t>
+          <t>669426</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1253356</t>
+          <t>1251941</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1311282</t>
+          <t>1310903</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,81%</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12974</t>
+          <t>13144</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30635</t>
+          <t>31840</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13106</t>
+          <t>12854</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>32276</t>
+          <t>31984</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32250</t>
+          <t>29563</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>57622</t>
+          <t>55689</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>30016</t>
+          <t>30417</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>57002</t>
+          <t>56020</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35690</t>
+          <t>35139</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>60969</t>
+          <t>60646</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>70715</t>
+          <t>72107</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>107556</t>
+          <t>109029</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>124314</t>
+          <t>126047</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>169936</t>
+          <t>170285</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>96512</t>
+          <t>97324</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>139414</t>
+          <t>137475</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>229912</t>
+          <t>231138</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>293413</t>
+          <t>289704</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,78%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>646560</t>
+          <t>643390</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>699031</t>
+          <t>696177</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>743034</t>
+          <t>746180</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>793736</t>
+          <t>795744</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1405043</t>
+          <t>1408440</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1478579</t>
+          <t>1476837</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>76,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,47%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>53218</t>
+          <t>51825</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>84891</t>
+          <t>84475</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>42059</t>
+          <t>41778</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>71573</t>
+          <t>72691</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>101897</t>
+          <t>103958</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>147136</t>
+          <t>149128</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>126328</t>
+          <t>125382</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>176381</t>
+          <t>175368</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>114838</t>
+          <t>112502</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>163163</t>
+          <t>159478</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>255200</t>
+          <t>253388</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>320951</t>
+          <t>321196</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,7 +6284,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>398574</t>
+          <t>399739</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>479198</t>
+          <t>479649</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>331061</t>
+          <t>332222</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>406838</t>
+          <t>406691</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>752929</t>
+          <t>759380</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>861708</t>
+          <t>864633</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,79%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2629858</t>
+          <t>2629213</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2721983</t>
+          <t>2721329</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2825308</t>
+          <t>2823744</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2918566</t>
+          <t>2917262</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>5480360</t>
+          <t>5477714</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>5602343</t>
+          <t>5606810</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,94%</t>
         </is>
       </c>
     </row>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7148</t>
+          <t>7125</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24100</t>
+          <t>23726</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3759</t>
+          <t>3319</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17526</t>
+          <t>15391</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12988</t>
+          <t>13342</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32393</t>
+          <t>33447</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29422</t>
+          <t>27940</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53494</t>
+          <t>54527</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12193</t>
+          <t>12379</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30597</t>
+          <t>29900</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>44330</t>
+          <t>45104</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>75830</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>99184</t>
+          <t>98930</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>137074</t>
+          <t>138843</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>70390</t>
+          <t>69196</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>104765</t>
+          <t>103657</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>177334</t>
+          <t>180083</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>233886</t>
+          <t>233903</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>456803</t>
+          <t>458590</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>500844</t>
+          <t>503055</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>70,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>519885</t>
+          <t>519612</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>557911</t>
+          <t>557447</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>988521</t>
+          <t>989682</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1048644</t>
+          <t>1048686</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,3%</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7456,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10380</t>
+          <t>10327</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27689</t>
+          <t>28524</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12820</t>
+          <t>12918</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31231</t>
+          <t>31905</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>27261</t>
+          <t>28694</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>53875</t>
+          <t>53149</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39819</t>
+          <t>41214</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>70408</t>
+          <t>72879</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30766</t>
+          <t>29987</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>56144</t>
+          <t>55462</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>77045</t>
+          <t>77854</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>116732</t>
+          <t>117428</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>154650</t>
+          <t>155412</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>205195</t>
+          <t>205299</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>137118</t>
+          <t>138038</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>184664</t>
+          <t>184406</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>303790</t>
+          <t>305509</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>375093</t>
+          <t>374309</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,39%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>731285</t>
+          <t>730052</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>788082</t>
+          <t>787260</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>771212</t>
+          <t>769179</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>827675</t>
+          <t>821065</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1520080</t>
+          <t>1517509</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1600935</t>
+          <t>1599035</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>78,57%</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>29742</t>
+          <t>28687</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>56672</t>
+          <t>55508</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23328</t>
+          <t>23076</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>46218</t>
+          <t>46135</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>58393</t>
+          <t>57760</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>94372</t>
+          <t>92386</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>74866</t>
+          <t>73952</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>113442</t>
+          <t>111859</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>82978</t>
+          <t>83681</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>121168</t>
+          <t>120141</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>165923</t>
+          <t>168296</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>218531</t>
+          <t>220456</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,6%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>148152</t>
+          <t>150245</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>192876</t>
+          <t>198144</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>139332</t>
+          <t>140100</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>186187</t>
+          <t>185941</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>304202</t>
+          <t>303144</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>370619</t>
+          <t>371442</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,59%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>416715</t>
+          <t>413576</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>471337</t>
+          <t>467191</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>437434</t>
+          <t>441298</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>492739</t>
+          <t>491988</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>868867</t>
+          <t>870279</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>949106</t>
+          <t>950921</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>62,96%</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6330</t>
+          <t>6851</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21172</t>
+          <t>20408</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13344</t>
+          <t>13241</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31472</t>
+          <t>30922</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23817</t>
+          <t>23795</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>46421</t>
+          <t>46969</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8684,7 +8684,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>26645</t>
+          <t>26111</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>49619</t>
+          <t>48997</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29546</t>
+          <t>28577</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>56164</t>
+          <t>55207</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>62119</t>
+          <t>61056</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>98625</t>
+          <t>95283</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>114939</t>
+          <t>114935</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>158521</t>
+          <t>157676</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>107822</t>
+          <t>110164</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>150974</t>
+          <t>153094</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>233196</t>
+          <t>235350</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>300177</t>
+          <t>297390</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,48%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>698884</t>
+          <t>700743</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>747710</t>
+          <t>750837</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>792227</t>
+          <t>793246</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>844308</t>
+          <t>841451</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1508615</t>
+          <t>1508614</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1580388</t>
+          <t>1578877</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9023,7 +9023,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,21%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>66590</t>
+          <t>65853</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>106513</t>
+          <t>104457</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>66442</t>
+          <t>67068</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>103984</t>
+          <t>103464</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>144016</t>
+          <t>143922</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>196546</t>
+          <t>195772</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9253,7 +9253,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>198356</t>
+          <t>195818</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>253029</t>
+          <t>253675</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>177889</t>
+          <t>176754</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>234205</t>
+          <t>231270</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>385127</t>
+          <t>382736</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>471062</t>
+          <t>466290</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>563243</t>
+          <t>562347</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>653347</t>
+          <t>651824</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>497471</t>
+          <t>503714</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>583278</t>
+          <t>587023</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1081251</t>
+          <t>1083554</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1211490</t>
+          <t>1206896</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2360253</t>
+          <t>2361957</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2463879</t>
+          <t>2462410</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>74,09%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2570296</t>
+          <t>2570031</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2671740</t>
+          <t>2668756</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>4951247</t>
+          <t>4962936</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>5106262</t>
+          <t>5106740</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,41%</t>
         </is>
       </c>
     </row>
@@ -9959,32 +9959,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3795</t>
+          <t>5418</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8319</t>
+          <t>11012</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9994,7 +9994,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>721</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -10004,12 +10004,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>824</t>
+          <t>3576</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -10019,7 +10019,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10029,32 +10029,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>3958</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1586</t>
+          <t>2678</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8611</t>
+          <t>11724</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -10072,32 +10072,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>31994</t>
+          <t>34322</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22142</t>
+          <t>24674</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44224</t>
+          <t>47516</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10107,32 +10107,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20742</t>
+          <t>21305</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13321</t>
+          <t>14893</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29738</t>
+          <t>31151</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10142,32 +10142,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>52736</t>
+          <t>55627</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39420</t>
+          <t>42261</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>67967</t>
+          <t>70658</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -10185,32 +10185,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>63703</t>
+          <t>66361</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>48100</t>
+          <t>51295</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>87775</t>
+          <t>84957</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10220,32 +10220,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>48956</t>
+          <t>50185</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>39293</t>
+          <t>40895</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>59881</t>
+          <t>60743</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10255,32 +10255,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>112659</t>
+          <t>116546</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>94654</t>
+          <t>99296</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>140641</t>
+          <t>140029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -10298,32 +10298,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>533233</t>
+          <t>581341</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>508907</t>
+          <t>560395</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>551607</t>
+          <t>599172</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10333,32 +10333,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>601774</t>
+          <t>656438</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>587863</t>
+          <t>642808</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>613063</t>
+          <t>668610</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10368,32 +10368,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1135008</t>
+          <t>1237779</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1106049</t>
+          <t>1211062</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1159500</t>
+          <t>1259856</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,97%</t>
         </is>
       </c>
     </row>
@@ -10411,17 +10411,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>632726</t>
+          <t>687442</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>632726</t>
+          <t>687442</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>632726</t>
+          <t>687442</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10446,17 +10446,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>671635</t>
+          <t>728649</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>671635</t>
+          <t>728649</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>671635</t>
+          <t>728649</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10481,17 +10481,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1304361</t>
+          <t>1416091</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1304361</t>
+          <t>1416091</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1304361</t>
+          <t>1416091</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10528,27 +10528,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2272</t>
+          <t>2252</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>585</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7166</t>
+          <t>6326</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -10563,32 +10563,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10203</t>
+          <t>10854</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5748</t>
+          <t>5952</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18030</t>
+          <t>18881</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10598,32 +10598,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>12475</t>
+          <t>13107</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6576</t>
+          <t>7873</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>20454</t>
+          <t>21181</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -10641,32 +10641,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>38784</t>
+          <t>40188</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17441</t>
+          <t>28245</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58109</t>
+          <t>55938</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10676,32 +10676,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>35136</t>
+          <t>37459</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24676</t>
+          <t>27427</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46958</t>
+          <t>48729</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10711,32 +10711,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>73921</t>
+          <t>77647</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50733</t>
+          <t>62319</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>97828</t>
+          <t>96907</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -10754,32 +10754,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>100754</t>
+          <t>109658</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49424</t>
+          <t>87290</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>141893</t>
+          <t>134856</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10789,32 +10789,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>92325</t>
+          <t>106863</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>77206</t>
+          <t>89978</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>111951</t>
+          <t>127579</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10824,32 +10824,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>193079</t>
+          <t>216522</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>130452</t>
+          <t>187073</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>235226</t>
+          <t>249253</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,84%</t>
         </is>
       </c>
     </row>
@@ -10867,32 +10867,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1038129</t>
+          <t>891375</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>986989</t>
+          <t>863110</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1114040</t>
+          <t>918348</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10902,32 +10902,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>812808</t>
+          <t>905971</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>791532</t>
+          <t>883808</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>831961</t>
+          <t>925665</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10937,32 +10937,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1850938</t>
+          <t>1797346</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1798709</t>
+          <t>1763166</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1940738</t>
+          <t>1831522</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>87,02%</t>
         </is>
       </c>
     </row>
@@ -10980,17 +10980,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1179939</t>
+          <t>1043474</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1179939</t>
+          <t>1043474</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1179939</t>
+          <t>1043474</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11015,17 +11015,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>950473</t>
+          <t>1061147</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>950473</t>
+          <t>1061147</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>950473</t>
+          <t>1061147</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11050,17 +11050,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2130413</t>
+          <t>2104621</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2130413</t>
+          <t>2104621</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2130413</t>
+          <t>2104621</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11097,32 +11097,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4850</t>
+          <t>4925</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1846</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11699</t>
+          <t>11232</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11132,32 +11132,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>8752</t>
+          <t>11139</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3104</t>
+          <t>5235</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17482</t>
+          <t>19959</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11167,32 +11167,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>13602</t>
+          <t>16064</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6915</t>
+          <t>8758</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24518</t>
+          <t>26030</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -11210,32 +11210,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>42253</t>
+          <t>41950</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29239</t>
+          <t>28448</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>60063</t>
+          <t>59885</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11245,32 +11245,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>32045</t>
+          <t>33838</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16235</t>
+          <t>24571</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>48398</t>
+          <t>46506</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11280,32 +11280,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>74298</t>
+          <t>75788</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>46490</t>
+          <t>59988</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>97061</t>
+          <t>96775</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -11323,32 +11323,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>124213</t>
+          <t>138538</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>98950</t>
+          <t>115153</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>152439</t>
+          <t>164780</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11358,32 +11358,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>96058</t>
+          <t>105193</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>48364</t>
+          <t>87452</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>132542</t>
+          <t>124866</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11393,32 +11393,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>220270</t>
+          <t>243731</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>145391</t>
+          <t>213626</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>268597</t>
+          <t>278325</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>17,31%</t>
         </is>
       </c>
     </row>
@@ -11436,32 +11436,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>531914</t>
+          <t>615113</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>500568</t>
+          <t>584830</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>559251</t>
+          <t>641049</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11471,32 +11471,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>795247</t>
+          <t>657196</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>746354</t>
+          <t>635083</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>866535</t>
+          <t>679667</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11506,32 +11506,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1327161</t>
+          <t>1272309</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1267787</t>
+          <t>1237343</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1444096</t>
+          <t>1312118</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>81,6%</t>
         </is>
       </c>
     </row>
@@ -11549,17 +11549,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>703230</t>
+          <t>800526</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>703230</t>
+          <t>800526</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>703230</t>
+          <t>800526</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11584,17 +11584,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>932102</t>
+          <t>807367</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>932102</t>
+          <t>807367</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>932102</t>
+          <t>807367</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11619,17 +11619,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1635332</t>
+          <t>1607893</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1635332</t>
+          <t>1607893</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1635332</t>
+          <t>1607893</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11666,32 +11666,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>17472</t>
+          <t>22978</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11008</t>
+          <t>14651</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25848</t>
+          <t>38292</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11701,32 +11701,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12057</t>
+          <t>13712</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6813</t>
+          <t>7952</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22787</t>
+          <t>24367</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11736,32 +11736,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>29529</t>
+          <t>36690</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>20675</t>
+          <t>25424</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>41226</t>
+          <t>52140</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -11779,32 +11779,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>61906</t>
+          <t>65753</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>46577</t>
+          <t>48998</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>83871</t>
+          <t>88903</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11814,32 +11814,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>47341</t>
+          <t>49579</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35362</t>
+          <t>39177</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>60471</t>
+          <t>62087</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11849,32 +11849,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>109247</t>
+          <t>115331</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>87643</t>
+          <t>93665</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>134581</t>
+          <t>142421</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -11892,32 +11892,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>102744</t>
+          <t>97873</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>82482</t>
+          <t>78333</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>130280</t>
+          <t>120753</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11927,32 +11927,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>95615</t>
+          <t>97028</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>74436</t>
+          <t>81181</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>113784</t>
+          <t>114647</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11962,32 +11962,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>198359</t>
+          <t>194901</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>169394</t>
+          <t>168652</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>230296</t>
+          <t>220415</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -12005,32 +12005,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>744546</t>
+          <t>802340</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>714389</t>
+          <t>777274</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>770859</t>
+          <t>829184</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12040,32 +12040,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>936279</t>
+          <t>955761</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>913970</t>
+          <t>934336</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>967367</t>
+          <t>976069</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12075,32 +12075,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1680825</t>
+          <t>1758102</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1642346</t>
+          <t>1722804</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1723496</t>
+          <t>1789897</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,03%</t>
         </is>
       </c>
     </row>
@@ -12118,17 +12118,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>926667</t>
+          <t>988944</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>926667</t>
+          <t>988944</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>926667</t>
+          <t>988944</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12153,17 +12153,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1091293</t>
+          <t>1116079</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1091293</t>
+          <t>1116079</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1091293</t>
+          <t>1116079</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12188,17 +12188,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2017960</t>
+          <t>2105024</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2017960</t>
+          <t>2105024</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2017960</t>
+          <t>2105024</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12235,32 +12235,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>28389</t>
+          <t>35573</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>19269</t>
+          <t>23959</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>40439</t>
+          <t>52349</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12270,32 +12270,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>31176</t>
+          <t>36426</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>21520</t>
+          <t>25876</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>45686</t>
+          <t>49570</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12305,32 +12305,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>59565</t>
+          <t>72000</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>45043</t>
+          <t>55471</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>78476</t>
+          <t>91209</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -12348,32 +12348,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>174937</t>
+          <t>182213</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>136284</t>
+          <t>153083</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>211155</t>
+          <t>212845</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12383,32 +12383,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>135265</t>
+          <t>142180</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>108165</t>
+          <t>121603</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>160076</t>
+          <t>162666</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12418,32 +12418,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>310202</t>
+          <t>324393</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>262268</t>
+          <t>287455</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>353856</t>
+          <t>359707</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -12461,27 +12461,27 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>391413</t>
+          <t>412430</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>298510</t>
+          <t>367894</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>446509</t>
+          <t>456422</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -12496,32 +12496,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>332954</t>
+          <t>359270</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>269730</t>
+          <t>326366</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>374290</t>
+          <t>394097</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12531,32 +12531,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>724367</t>
+          <t>771701</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>629137</t>
+          <t>720145</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>805738</t>
+          <t>830108</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,48%</t>
         </is>
       </c>
     </row>
@@ -12574,32 +12574,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2847823</t>
+          <t>2890169</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2779826</t>
+          <t>2838377</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2985654</t>
+          <t>2938204</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12609,32 +12609,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3146110</t>
+          <t>3175367</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3092690</t>
+          <t>3131070</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3237998</t>
+          <t>3210141</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12644,32 +12644,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>5993932</t>
+          <t>6065536</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>5893546</t>
+          <t>5999305</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6131086</t>
+          <t>6129401</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>84,73%</t>
         </is>
       </c>
     </row>
@@ -12687,17 +12687,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3442562</t>
+          <t>3520386</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3442562</t>
+          <t>3520386</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3442562</t>
+          <t>3520386</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12722,17 +12722,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3645504</t>
+          <t>3713243</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3645504</t>
+          <t>3713243</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3645504</t>
+          <t>3713243</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12757,17 +12757,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>7088066</t>
+          <t>7233629</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7088066</t>
+          <t>7233629</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7088066</t>
+          <t>7233629</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
